--- a/artfynd/S 3190-2022 artfynd.xlsx
+++ b/artfynd/S 3190-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY258"/>
+  <dimension ref="A1:AZ258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328007</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328016</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328070</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328077</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328110</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440061</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440062</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440063</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440064</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440065</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448435</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448438</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1963,6 +2028,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448440</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2070,6 +2140,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448444</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2177,6 +2252,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448542</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2284,6 +2364,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448545</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2391,6 +2476,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448769</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2498,6 +2588,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448871</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2605,6 +2700,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448546</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2702,6 +2802,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440097</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2809,6 +2914,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448477</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2916,6 +3026,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448484</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3023,6 +3138,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448487</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3130,6 +3250,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448497</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3237,6 +3362,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448503</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3344,6 +3474,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448515</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3451,6 +3586,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448511</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3558,6 +3698,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448812</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3665,6 +3810,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448853</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3762,6 +3912,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328114</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3859,6 +4014,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440094</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3956,6 +4116,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440095</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4053,6 +4218,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70327988</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4179,6 +4349,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448551</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4301,6 +4476,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448461</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4423,6 +4603,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448896</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4520,6 +4705,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440066</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4627,6 +4817,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448840</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4724,6 +4919,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328033</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4821,6 +5021,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328112</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4918,6 +5123,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440090</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5015,6 +5225,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440091</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5112,6 +5327,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440092</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5219,6 +5439,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448436</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5326,6 +5551,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448437</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5433,6 +5663,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448439</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5540,6 +5775,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448442</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5647,6 +5887,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448446</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5754,6 +5999,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448454</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5861,6 +6111,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448455</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5968,6 +6223,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448459</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6075,6 +6335,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448469</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6182,6 +6447,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448470</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6289,6 +6559,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448473</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6396,6 +6671,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448474</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6503,6 +6783,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448476</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6610,6 +6895,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448481</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6717,6 +7007,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448485</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6824,6 +7119,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448489</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6931,6 +7231,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448490</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7038,6 +7343,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448493</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7145,6 +7455,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448495</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7252,6 +7567,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448501</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7359,6 +7679,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448504</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7466,6 +7791,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448505</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7573,6 +7903,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448510</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7680,6 +8015,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448512</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7787,6 +8127,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448513</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7894,6 +8239,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448514</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8001,6 +8351,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448516</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8108,6 +8463,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448518</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8215,6 +8575,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448521</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8322,6 +8687,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448524</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8429,6 +8799,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448526</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8536,6 +8911,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448531</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8643,6 +9023,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448533</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8750,6 +9135,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448540</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8857,6 +9247,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448556</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8964,6 +9359,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448767</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9071,6 +9471,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448768</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9178,6 +9583,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448770</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9285,6 +9695,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448773</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9392,6 +9807,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448777</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9499,6 +9919,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448778</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9606,6 +10031,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448811</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9713,6 +10143,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448813</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9820,6 +10255,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448815</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9927,6 +10367,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448816</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10034,6 +10479,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448817</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10141,6 +10591,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448818</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10248,6 +10703,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448820</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10355,6 +10815,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448822</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10462,6 +10927,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448825</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10569,6 +11039,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448827</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10676,6 +11151,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448829</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10783,6 +11263,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448831</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10890,6 +11375,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448835</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10997,6 +11487,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448837</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11104,6 +11599,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448838</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11211,6 +11711,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448843</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11318,6 +11823,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448849</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11425,6 +11935,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448852</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11532,6 +12047,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448854</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11639,6 +12159,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448855</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11746,6 +12271,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448857</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11853,6 +12383,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448859</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11960,6 +12495,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448862</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12067,6 +12607,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448863</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12174,6 +12719,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448864</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12281,6 +12831,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448868</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12388,6 +12943,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448869</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12495,6 +13055,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448870</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12602,6 +13167,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448875</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12709,6 +13279,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448877</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12816,6 +13391,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448878</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12923,6 +13503,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448882</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13030,6 +13615,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448883</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13137,6 +13727,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448885</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13244,6 +13839,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448887</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13366,6 +13966,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448889</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13473,6 +14078,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448890</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13580,6 +14190,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448894</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13687,6 +14302,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448895</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13794,6 +14414,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448899</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13901,6 +14526,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448901</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13998,6 +14628,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440080</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14095,6 +14730,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440081</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14202,6 +14842,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448488</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14309,6 +14954,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448494</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14406,6 +15056,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328084</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14503,6 +15158,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70327987</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14600,6 +15260,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70327991</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14697,6 +15362,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328023</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14794,6 +15464,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328027</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14891,6 +15566,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328062</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14988,6 +15668,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328104</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15085,6 +15770,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328113</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15182,6 +15872,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440050</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15279,6 +15974,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440051</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15376,6 +16076,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440052</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15473,6 +16178,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440053</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15570,6 +16280,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440054</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15667,6 +16382,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440055</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15764,6 +16484,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440056</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15861,6 +16586,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440057</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15968,6 +16698,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448447</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16075,6 +16810,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448456</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16182,6 +16922,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448457</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16289,6 +17034,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448458</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16396,6 +17146,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448520</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16503,6 +17258,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448523</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16610,6 +17370,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448528</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16717,6 +17482,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448530</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16824,6 +17594,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448534</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16931,6 +17706,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448536</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17038,6 +17818,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448550</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17145,6 +17930,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448553</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17252,6 +18042,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448772</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17359,6 +18154,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448774</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17466,6 +18266,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448821</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17573,6 +18378,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448828</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17680,6 +18490,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448830</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17787,6 +18602,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448833</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17894,6 +18714,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448834</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18001,6 +18826,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448839</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18108,6 +18938,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448842</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18215,6 +19050,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448850</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18322,6 +19162,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448860</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18429,6 +19274,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448865</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18536,6 +19386,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448867</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18633,6 +19488,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70327997</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18730,6 +19590,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328054</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18827,6 +19692,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440083</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18924,6 +19794,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440084</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19021,6 +19896,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440085</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19128,6 +20008,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448480</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19235,6 +20120,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448492</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19342,6 +20232,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448881</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19449,6 +20344,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448892</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19546,6 +20446,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440068</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19643,6 +20548,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440069</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19740,6 +20650,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440070</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19837,6 +20752,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440071</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19944,6 +20864,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448471</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20051,6 +20976,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448478</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20158,6 +21088,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448479</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20265,6 +21200,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448482</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20372,6 +21312,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448496</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20479,6 +21424,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448876</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -20586,6 +21536,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448879</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -20693,6 +21648,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448884</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20815,6 +21775,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448537</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20937,6 +21902,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448464</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21059,6 +22029,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448897</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21166,6 +22141,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448544</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21273,6 +22253,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448898</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21395,6 +22380,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448460</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21502,6 +22492,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448465</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -21624,6 +22619,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448466</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -21746,6 +22746,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448538</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -21856,6 +22861,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440078</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -21968,6 +22978,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448449</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22080,6 +23095,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448508</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -22192,6 +23212,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448527</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -22304,6 +23329,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448539</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -22416,6 +23446,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448846</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -22528,6 +23563,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448858</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -22630,6 +23670,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328041</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -22740,6 +23785,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440074</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -22857,6 +23907,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448441</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -22969,6 +24024,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448443</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -23086,6 +24146,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448445</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -23203,6 +24268,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448448</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -23320,6 +24390,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448453</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -23437,6 +24512,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448506</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -23554,6 +24634,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448509</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -23671,6 +24756,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448522</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -23783,6 +24873,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448525</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -23900,6 +24995,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448535</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -24017,6 +25117,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448776</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -24129,6 +25234,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448823</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -24241,6 +25351,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448824</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -24358,6 +25473,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448826</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -24475,6 +25595,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448836</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -24587,6 +25712,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448844</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -24704,6 +25834,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448856</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -24821,6 +25956,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448861</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -24938,6 +26078,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448873</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -25055,6 +26200,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448874</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -25172,6 +26322,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448888</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -25284,6 +26439,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448450</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -25396,6 +26556,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448451</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -25508,6 +26673,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448467</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -25620,6 +26790,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448468</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -25732,6 +26907,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448475</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -25844,6 +27024,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448507</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -25956,6 +27141,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448555</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -26068,6 +27258,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448775</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -26180,6 +27375,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448851</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -26292,6 +27492,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448891</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -26404,6 +27609,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448900</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -26501,6 +27711,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328111</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -26613,6 +27828,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448845</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -26725,6 +27945,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448866</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -26837,6 +28062,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448517</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -26952,6 +28182,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448947</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -27049,6 +28284,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328096</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -27146,6 +28386,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440082</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -27253,6 +28498,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448819</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -27360,6 +28610,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448847</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -27457,6 +28712,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328055</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -27564,6 +28824,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448483</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -27671,6 +28936,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448486</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -27778,6 +29048,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448491</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -27885,6 +29160,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448500</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -27982,6 +29262,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328015</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -28079,8 +29364,272 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440072</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>